--- a/AAII_Financials/Quarterly/NGG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NGG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>NGG</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43190</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43008</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42825</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42643</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42460</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42277</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42094</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7013000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>7148000</v>
+      </c>
+      <c r="F8" s="3">
         <v>4748400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4839700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>6729400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>6520700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>5335100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5030500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>7174300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>7235600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5179600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5393900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>7555800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>9108000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>9974000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>7732200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>10456500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>7803400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>10156400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7742700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>11682200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>9458600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>11563500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>7734400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>17232500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>8939700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>17588400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>8380100</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -938,49 +950,55 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7013000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7148000</v>
+      </c>
+      <c r="F10" s="3">
         <v>4748400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4839700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>6729400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>6520700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>5335100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5030500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>7174300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>7235600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>5179600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>5393900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>7555800</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
@@ -1021,8 +1039,14 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1052,49 +1076,51 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>27800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>26900</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>20200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>20400</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="N12" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N12" s="3">
-        <v>14200</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>5</v>
+      <c r="P12" s="3">
+        <v>14200</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>5</v>
@@ -1135,8 +1161,14 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1218,133 +1250,145 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-335400</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-341900</v>
+      </c>
+      <c r="F14" s="3">
         <v>87400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>89100</v>
       </c>
-      <c r="F14" s="3">
-        <v>-27800</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-26900</v>
-      </c>
       <c r="H14" s="3">
+        <v>-55600</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-53800</v>
+      </c>
+      <c r="J14" s="3">
         <v>28800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>27200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>662400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>668100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-25600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-26700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-155900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>211300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>274200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-19100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>148300</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>311100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>273300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>-347800</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>836100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>995100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB14" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>172500</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>498500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>508100</v>
+      </c>
+      <c r="F15" s="3">
         <v>740700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>754900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>481900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>467000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>709000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>668500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>421800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>425400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>623000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>648700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>434900</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1384,8 +1428,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1412,174 +1462,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4726600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4817600</v>
+      </c>
+      <c r="F17" s="3">
         <v>3601800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3671100</v>
       </c>
-      <c r="F17" s="3">
-        <v>4383800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4247800</v>
-      </c>
       <c r="H17" s="3">
+        <v>4411600</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4274700</v>
+      </c>
+      <c r="J17" s="3">
         <v>4395500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4144600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4906000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4947900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3963000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4126900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6106500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7150200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>8083200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>6508100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>8204500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>6558900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>7964500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>6502100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>8656000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>7655700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>9270600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>5921500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>13026100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>6528100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>13875000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>6225800</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2286400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2330400</v>
+      </c>
+      <c r="F18" s="3">
         <v>1146600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1168700</v>
       </c>
-      <c r="F18" s="3">
-        <v>2345600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>2272900</v>
-      </c>
       <c r="H18" s="3">
+        <v>2317900</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2246000</v>
+      </c>
+      <c r="J18" s="3">
         <v>939600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>885900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>2268300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2287700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1216700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1267000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1449300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1957800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1890900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1224100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>2252000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1244500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>2191900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1240600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>3026300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1802900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>2292900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1812900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>4206400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>2411700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>3713300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>2154300</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1609,423 +1673,455 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F20" s="3">
         <v>57100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>58200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>16800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>16300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>12700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>12000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>61300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>61800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-28700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-29900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-62500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>101000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-80000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-2600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>7600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-76900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-104100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-17100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>222300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-9900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-30400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-142900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-293500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-148700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-96100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-55300</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2773700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2827100</v>
+      </c>
+      <c r="F21" s="3">
         <v>1830100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1865300</v>
       </c>
-      <c r="F21" s="3">
-        <v>2810800</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2723600</v>
-      </c>
       <c r="H21" s="3">
+        <v>2783000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2696600</v>
+      </c>
+      <c r="J21" s="3">
         <v>1635800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1542500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2628900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2651300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1868300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1945600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1946600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>3161100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3006300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2191900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>3282300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>2201200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>3030600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2188500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>4295900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>2871300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>3284800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>2540800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>5622900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>3301200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>5200000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>3048400</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>465500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>474400</v>
+      </c>
+      <c r="F22" s="3">
         <v>551800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>562400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>544600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>527700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>560900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>528900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>528600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>533100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>478400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>498200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>510300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>637700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>392300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>478200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>548700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>666300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>527600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>586800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>684600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>689200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>652500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>481600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>875200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>504800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>1036300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>551700</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2215800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2258400</v>
+      </c>
+      <c r="F23" s="3">
         <v>555200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>565800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1916000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1856600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>458400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>432200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1059000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1068000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>836500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>871100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1190100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1421100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1418500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>743400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1710900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>501300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1560200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>636800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>2563900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1103800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1610000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1188500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>3037700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1758200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>2580900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>1547200</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>482600</v>
+      </c>
+      <c r="E24" s="3">
+        <v>491900</v>
+      </c>
+      <c r="F24" s="3">
         <v>139800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>142500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>458000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>443800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>75100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>70800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>330900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>333700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>187300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>195100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>265400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>927700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>353000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>116000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>588000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>19900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>291000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>113500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>638300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>216500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>319600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>162600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>556900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>390000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>614900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>356900</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2107,174 +2203,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1733100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1766500</v>
+      </c>
+      <c r="F26" s="3">
         <v>415400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>423300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1458000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1412800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>383300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>361400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>728100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>734300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>649200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>676100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>924800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>493400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1065500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>627300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1122800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>481400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1269300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>523300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1925700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>887300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1290400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>1025900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>2480800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>1368200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>1966000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>1190400</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1732500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1765800</v>
+      </c>
+      <c r="F27" s="3">
         <v>414700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>422700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1456700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1411500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>433600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>408800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>733800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>740100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>688300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>716700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>4046000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>493400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1064200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>626100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1122800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>480200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1266900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>522100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1925700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>885900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1290400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>1023500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>2479500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>1365600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>1979100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>1195600</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2356,8 +2470,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2374,73 +2494,79 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>50900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>48000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>5700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>5700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>39700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>41300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>3121300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>129900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>297900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>140300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-19000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>7400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>10600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>3700</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>1993900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>70800</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>8339500</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>-405200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>900000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>679500</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>679500</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2522,8 +2648,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2605,174 +2737,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-57100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-58200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-16800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-16300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-12700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-12000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-61300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-61800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>28700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>29900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>62500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-101000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>80000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>2600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-7600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>76900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>104100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>17100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-222300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>9900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>30400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>142900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>293500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>148700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>96100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>55300</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1732500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1765800</v>
+      </c>
+      <c r="F33" s="3">
         <v>414700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>422700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1456700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1411500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>433600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>408800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>733800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>740100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>688300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>716700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>4046000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>623300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1362100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>766300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1103800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>487600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1277500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>525800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>3919500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>956600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>9629900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>618300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>3379500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1365600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>2658600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>1195600</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2854,179 +3004,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1732500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1765800</v>
+      </c>
+      <c r="F35" s="3">
         <v>414700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>422700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1456700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1411500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>433600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>408800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>733800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>740100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>688300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>716700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>4046000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>623300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1362100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>766300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1103800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>487600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1277500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>525800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>3919500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>956600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>9629900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>618300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>3379500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1365600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>2658600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>1195600</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43190</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43008</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42825</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42643</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42460</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42277</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42094</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3056,8 +3224,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3087,755 +3257,811 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>495200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>504700</v>
+      </c>
+      <c r="F41" s="3">
         <v>1192300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1215200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1522000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1474800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1507800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1421800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>706000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>712000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>277000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>288500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>201700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>611500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>206000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>209100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>92500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>264300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>298100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>158600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>448700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>55200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1504400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>199500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>165600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>150000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>156700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>453000</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3239100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3301500</v>
+      </c>
+      <c r="F42" s="3">
         <v>4263800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>4345800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>7432900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>7202300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>8229500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>7759700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>4671800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>4711600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2050100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2134900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3222700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>3002300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>3073200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1676800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>2532100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>4226200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>2343300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>2022600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>3674100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>3641100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>11545000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>4008900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>3910300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>3096400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>3369700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>4334900</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4683700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4773900</v>
+      </c>
+      <c r="F43" s="3">
         <v>3818900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3892300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4861800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4711000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3592000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3387000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3840700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3873500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4097800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4267300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4310200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3973300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3918200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3584300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>3913400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3126800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3878700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2957000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>3971400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>3094800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>4021800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2880700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>3224300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2796400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>3734400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>2486100</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>738100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>752400</v>
+      </c>
+      <c r="F44" s="3">
         <v>861600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>878200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>719600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>697300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>856500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>807600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1045700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1054700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1136100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1183100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>915500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>677100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>576100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>638800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>695700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>579500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>437700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>536800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>465100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>663700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>532300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>549300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>570000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>515200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>447700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>563600</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>283900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>289400</v>
+      </c>
+      <c r="F45" s="3">
         <v>1863100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1898900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3541400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3431500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5195000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4898500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2358000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2378100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1831700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1907500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2142700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>13375300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>5267200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>68900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>117900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>125300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2441500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2818000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>552300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>849100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>324900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>268500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>362600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>230900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>233100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>267300</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9883700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10074000</v>
+      </c>
+      <c r="F46" s="3">
         <v>11999600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>12230400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>18517000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>17942600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>19380800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>18274400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>13108400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>13220300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>9392800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>9781300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>11274000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>21639500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>13040600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>6177900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>7351600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>8322000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>9399300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>8492900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>9111500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>8303900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>17928400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>7906900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>8232800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>6788900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>7941600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>8104800</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1935800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1973100</v>
+      </c>
+      <c r="F47" s="3">
         <v>1907400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1944100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1816600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1760200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2273200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2143400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2904800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2929600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2788400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2903800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2671000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2394800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>2128400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>2087300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1949100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1907100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1508200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1565100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>4182700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>4793000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>4204100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1210700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>1146500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>996500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>853300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>836200</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>107644900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>109717400</v>
+      </c>
+      <c r="F48" s="3">
         <v>102622500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>104596500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>95726000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>92756400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>92742300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>87448000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>87028000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>87770700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>82244400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>85646400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>79712200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>71776000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>61729800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>62675000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>63063400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>58847400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>51944700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>52042200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>54351100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>55875600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>52600500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>57282900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>56560100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>54091000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>53623600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>50500200</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17557000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>17895000</v>
+      </c>
+      <c r="F49" s="3">
         <v>17490700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>17827100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>16920100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>16395200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>17102300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>16126000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>16620800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>16762600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>16623100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>17310700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>16640700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>16641300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>7913900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>9470200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>8880000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>9306000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>8224700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>8356300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>8650500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>9328400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>9270600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>8395800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>8089300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>7688900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>7831000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>7125200</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3917,8 +4143,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4000,91 +4232,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5960600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6075400</v>
+      </c>
+      <c r="F52" s="3">
         <v>5453400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>5558300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>4931600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>4778600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>5014100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>4727800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>4520200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>4558800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3962400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>4126300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4380700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4252800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3388100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3459300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>4374700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>3860100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>3402000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3670700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3877300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>3216500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2957200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2703400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2839500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2156000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2291200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2156900</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4166,91 +4410,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>142982000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>145734900</v>
+      </c>
+      <c r="F54" s="3">
         <v>139473600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>142156500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>137911300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>133633000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>136512500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>128719700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>124182200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>125242000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>115011100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>119768500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>114678600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>116704400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>88200800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>83869700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>85618800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>82242700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>74478900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>74127200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>80173100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>81517400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>86960800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>77499700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>76868200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>71721400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>72540600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>68723300</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4280,8 +4536,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4311,506 +4569,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4455300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4541000</v>
+      </c>
+      <c r="F57" s="3">
         <v>5731600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5841900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3830800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3712000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>5319700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5016000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3518700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3548700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>5448700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5674100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4019400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4876100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>4615000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>4235900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>4564800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>4308100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4458400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>3835400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>4709200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>4078300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>4418000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3861100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>4284700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3731600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>4334900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3501300</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5462800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5568000</v>
+      </c>
+      <c r="F58" s="3">
         <v>5352600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>5455500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>6482000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>6280900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3622800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3416000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6451300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6506300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3675600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>3827600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3770800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>14098300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>4903700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2730000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>5160400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>6232500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>5289900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>5043100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>6064800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>5468000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>7259100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>5109900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>4709900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>3782500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3987200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3697500</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2893200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2948900</v>
+      </c>
+      <c r="F59" s="3">
         <v>1262200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1286500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3240400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3139800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3101500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2924400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>4414100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>4451800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>978700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1019200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3207900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12423900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2774000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>851800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1127900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1294200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1050400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1155200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1086900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1256600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2205700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1576400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1076100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1006900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1387900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1223300</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12936700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>13185700</v>
+      </c>
+      <c r="F60" s="3">
         <v>12346400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>12583900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>13722400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>13296700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>12044000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>11356400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>14384000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>14506800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10103000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>10520900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>11295000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>31398300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>12292700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>7817600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>10853200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>11834800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>10798700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>10033700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>11860900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>10802900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>13882800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>10547400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>10070600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>8521100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>9710000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>8422200</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>57530300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>58638000</v>
+      </c>
+      <c r="F61" s="3">
         <v>57592000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>58699800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>56409000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>54659000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>58071300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>54756300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>54421700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>54886100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>52744500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>54926200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>50791800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>43500700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>36063200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>38101300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>33864800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>32567300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>28694800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>28679800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>30246100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>31479100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>30565700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>34582100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>32259500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>30991700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>30130800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>30009600</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4596600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4685100</v>
+      </c>
+      <c r="F62" s="3">
         <v>4749000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>4840400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>4651200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4506900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>4708500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>4439700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>4688200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4728200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>4184500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4357600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>4003400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>14720300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>13784700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>14561600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>15817200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>14245600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>12073900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>11826900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>12361400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>15359600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>15589300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>16888900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>16845200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>16153900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>16932600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>14330600</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4892,8 +5188,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4975,8 +5277,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5058,91 +5366,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91047900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>92800800</v>
+      </c>
+      <c r="F66" s="3">
         <v>89445400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>91165900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>89039900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>86277700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>88441200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>83392500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>86429300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>87166900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>79036200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>82305500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>78106400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>89646900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>62168100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>60508600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>60563000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>58675000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>51591000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>50562400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>54490200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>57664300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>60059000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>62034500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>59188300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>55678400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>56789200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>52771700</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5172,8 +5492,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5255,8 +5577,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5338,8 +5666,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5421,8 +5755,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5504,91 +5844,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>55339700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>56405100</v>
+      </c>
+      <c r="F72" s="3">
         <v>53747600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>54781500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>51817200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>50209700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>51829500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>48870800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>40498600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>40844200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>38134900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>39712300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>39103300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>31016500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>30394500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>26610100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>27747500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>25965000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>25803800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>26334000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>29456500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>27308800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>29826100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>18541700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>21266800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>19880300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>19580700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>19807200</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5670,8 +6022,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5753,8 +6111,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5836,91 +6200,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51893200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>52892300</v>
+      </c>
+      <c r="F76" s="3">
         <v>49990600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>50952200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>48841700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>47326500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>48037800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>45295500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>37721300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>38043300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>35944400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>37431200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>36542500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>27057600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>26032700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>23361100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>25055800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>23567800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>22887900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>23564800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>25682900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>23853100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>26901900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>15465200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>17679900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>16043000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>15751400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>15951600</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6002,179 +6378,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43190</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43008</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42825</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42643</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42460</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42277</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42094</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1732500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1765800</v>
+      </c>
+      <c r="F81" s="3">
         <v>414700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>422700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1456700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1411500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>433600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>408800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>733800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>740100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>688300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>716700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>4046000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>623300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1362100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>766300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1103800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>487600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1277500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>525800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>3919500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>956600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>9629900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>618300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>3379500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1365600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>2658600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>1195600</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6204,91 +6598,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>559400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>542100</v>
+      </c>
+      <c r="F83" s="3">
         <v>627300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>591500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>494500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>498700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>623000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>648700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>515300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>501800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>519300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>566300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>852500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1102200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1074700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1087700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1022700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1033600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>942800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>964900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1047400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>1078300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>813600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>1065300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>2105200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1038200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>1967300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>949400</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6370,8 +6772,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6453,8 +6861,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6536,8 +6950,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6619,8 +7039,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6702,91 +7128,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2775000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2828400</v>
+      </c>
+      <c r="F89" s="3">
         <v>2437000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>2483900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2710600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>2626500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1750400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1650500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2575200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2597200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1745700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1817900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>2703100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>3159800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>3494400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2287500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>3381200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>2419600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2874400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2303200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>3492700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2748100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>4168400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2571600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>7001500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>3290800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>6593200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>3195800</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6816,91 +7254,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3661000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-3731500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2986800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-3044300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-3097600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-3001500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2670600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2518100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2332700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2352600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1958600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2039600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1897100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2506000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2536000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-2252000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2649000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-2251000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-2212000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2153100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-2686700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2501900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-2310100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-1905300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-3723800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-2279900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-7942900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-1809300</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6982,8 +7428,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7065,91 +7517,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2390700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2436700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-360200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-367200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2697100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2613400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-4286300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4041600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-3213600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-3241100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1470500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1531300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>535700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-13784700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-4469400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-2180400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1761500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-2239600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-2749100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-866100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-2730300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>5998700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-2977100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-2537100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-5264200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1762100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-2634900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-1310200</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7179,91 +7643,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>481300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>490600</v>
+      </c>
+      <c r="F96" s="3">
         <v>600900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>612400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>463800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>449400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>543500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>512500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>248200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>250300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>808500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>841900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>301900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-765000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-456600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-1358000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-424500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-691100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-532300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-866100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-471900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-5860000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-713200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-1136800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-1743900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-1050000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-1673600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-974400</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7345,8 +7817,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7428,8 +7906,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7511,253 +7995,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-802200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-817600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2288500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2332500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-34200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-33200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>3070000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2894700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>868300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>875700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-236700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-246500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-3301900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>11029000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>972300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>11500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1792000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-238200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>18900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1683500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-364100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-10302000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>96400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1732100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1539100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-4283500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1908000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>26300</v>
+      </c>
+      <c r="F101" s="3">
         <v>-43600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-41100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-4900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-4800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>8400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>9100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>2600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>1300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-2600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-5100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>9900</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>3700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-2700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-1400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>2600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>17200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>5200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>31600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-418600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-426600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-216400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-220600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>6500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>6300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>490600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>462500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>228600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>230500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>39100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>40700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-68000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>405500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>116000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-177400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-48400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>144300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-242800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>395500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1556600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1290400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>46800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>10400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-293600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-13200</v>
       </c>
     </row>
